--- a/Data/Coordenadores_EF/Coordenadores (SP-RJ-Santos).xlsx
+++ b/Data/Coordenadores_EF/Coordenadores (SP-RJ-Santos).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/rjuan_mgcontecnica_com_br/Documents/Área de Trabalho/Python/Controle de impostos/Data/Coordenadores_EF/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{7A913EE7-9821-411D-908D-3CDF5817F2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB9DC98D-7680-42A0-80B0-082841FC5DAB}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{7A913EE7-9821-411D-908D-3CDF5817F2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E58C9FA7-685C-40AA-860E-047B42B66543}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -3503,7 +3503,7 @@
         <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>118</v>
+        <v>461</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
